--- a/outputs/tabel/tabel_13_perbandingan_arsitektur_lstm_dan_gru_terbaik.xlsx
+++ b/outputs/tabel/tabel_13_perbandingan_arsitektur_lstm_dan_gru_terbaik.xlsx
@@ -543,12 +543,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>79.56</t>
+          <t>143.72</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>83.05</t>
+          <t>150.39</t>
         </is>
       </c>
     </row>
@@ -560,12 +560,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.2874</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.3008</t>
         </is>
       </c>
     </row>
